--- a/Honda_Logi/Excel_Format/部品単位包装費一覧(外装).xlsx
+++ b/Honda_Logi/Excel_Format/部品単位包装費一覧(外装).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F769ACF-7844-4291-967C-3792825353AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F94BAD-D00E-4752-9B9B-A071C4338A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{C1A7F913-9E96-44AA-8817-2897826344C9}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{C1A7F913-9E96-44AA-8817-2897826344C9}"/>
   </bookViews>
   <sheets>
     <sheet name="部品単位包装費一覧(外装)" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +121,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -219,12 +227,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -253,16 +264,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -635,9 +644,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="4" width="11.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="10" customWidth="1"/>
-    <col min="6" max="9" width="11.125" style="11" customWidth="1"/>
+    <col min="2" max="5" width="11.125" style="9" customWidth="1"/>
+    <col min="6" max="9" width="11.125" style="10" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
